--- a/docs/Machine States.xlsx
+++ b/docs/Machine States.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/15a35a7ae5f87534/Escritorio/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\sme\sme-stm32f407-4wcl\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="69" documentId="8_{8CE449DF-404C-4194-A490-E60F52E1B456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0D2CC98-3C52-4348-88CA-869E7478DFD3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F271281-7AFD-48F9-A19A-CF91CB86E470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5F656E1E-D535-46EA-9279-56770E9D3720}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{5F656E1E-D535-46EA-9279-56770E9D3720}"/>
   </bookViews>
   <sheets>
     <sheet name="Main State" sheetId="1" r:id="rId1"/>
+    <sheet name="Errors Table" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="125">
   <si>
     <t>Comando UART</t>
   </si>
@@ -183,6 +184,234 @@
   </si>
   <si>
     <t>Event transition table</t>
+  </si>
+  <si>
+    <t>Categoría</t>
+  </si>
+  <si>
+    <t>Bit</t>
+  </si>
+  <si>
+    <t>Nombre del Flag</t>
+  </si>
+  <si>
+    <t>RTOS</t>
+  </si>
+  <si>
+    <t>0x0000000000000001</t>
+  </si>
+  <si>
+    <t>ERR_RTOS_TASK</t>
+  </si>
+  <si>
+    <t>0x0000000000000002</t>
+  </si>
+  <si>
+    <t>ERR_RTOS_QUEUE</t>
+  </si>
+  <si>
+    <t>0x0000000000000004</t>
+  </si>
+  <si>
+    <t>ERR_RTOS_TIMER</t>
+  </si>
+  <si>
+    <t>0x0000000000000008</t>
+  </si>
+  <si>
+    <t>ERR_RTOS_MUTEX</t>
+  </si>
+  <si>
+    <t>HAL (FW)</t>
+  </si>
+  <si>
+    <t>0x0000000000000100</t>
+  </si>
+  <si>
+    <t>ERR_HAL_ADC</t>
+  </si>
+  <si>
+    <t>0x0000000000000200</t>
+  </si>
+  <si>
+    <t>ERR_HAL_UART</t>
+  </si>
+  <si>
+    <t>0x0000000000000400</t>
+  </si>
+  <si>
+    <t>ERR_HAL_I2C</t>
+  </si>
+  <si>
+    <t>0x0000000000000800</t>
+  </si>
+  <si>
+    <t>ERR_HAL_SPI</t>
+  </si>
+  <si>
+    <t>BSP</t>
+  </si>
+  <si>
+    <t>0x0000000001000000</t>
+  </si>
+  <si>
+    <t>ERR_BSP_LED</t>
+  </si>
+  <si>
+    <t>0x0000000002000000</t>
+  </si>
+  <si>
+    <t>ERR_BSP_BUTTON</t>
+  </si>
+  <si>
+    <t>0x0000000004000000</t>
+  </si>
+  <si>
+    <t>ERR_BSP_BUZZER</t>
+  </si>
+  <si>
+    <t>Lógica</t>
+  </si>
+  <si>
+    <t>0x0000000100000000</t>
+  </si>
+  <si>
+    <t>ERR_BATT_LOW</t>
+  </si>
+  <si>
+    <t>0x0000000200000000</t>
+  </si>
+  <si>
+    <t>ERR_OVER_TEMP</t>
+  </si>
+  <si>
+    <t>0x0000000400000000</t>
+  </si>
+  <si>
+    <t>ERR_HEARTBEAT</t>
+  </si>
+  <si>
+    <t>FATAL</t>
+  </si>
+  <si>
+    <t>0x8000000000000000</t>
+  </si>
+  <si>
+    <t>ERR_SYS_PANIC</t>
+  </si>
+  <si>
+    <t>Valor Hexadecimal (64-bit)</t>
+  </si>
+  <si>
+    <t>Descripción / Uso</t>
+  </si>
+  <si>
+    <t>Fallo al crear una tarea de FreeRTOS.</t>
+  </si>
+  <si>
+    <t>Fallo al inicializar una cola de mensajes.</t>
+  </si>
+  <si>
+    <t>Fallo al crear un temporizador de software.</t>
+  </si>
+  <si>
+    <t>Fallo al crear un Mutex o Semáforo.</t>
+  </si>
+  <si>
+    <t>0x00...0010 - 0x00...0080</t>
+  </si>
+  <si>
+    <t>Reservado</t>
+  </si>
+  <si>
+    <t>Reservado para RTOS/IPC adicional.</t>
+  </si>
+  <si>
+    <t>Error en el periférico ADC (STM32 HAL).</t>
+  </si>
+  <si>
+    <t>Error en el periférico UART (STM32 HAL).</t>
+  </si>
+  <si>
+    <t>Error en el bus I2C (STM32 HAL).</t>
+  </si>
+  <si>
+    <t>Error en el bus SPI (STM32 HAL).</t>
+  </si>
+  <si>
+    <t>0x0000000000001000</t>
+  </si>
+  <si>
+    <t>ERR_HAL_FLASH</t>
+  </si>
+  <si>
+    <t>Error de acceso a Flash (Lectura/Escritura).</t>
+  </si>
+  <si>
+    <t>13-23</t>
+  </si>
+  <si>
+    <t>0x00...2000 - 0x0080...</t>
+  </si>
+  <si>
+    <t>Reservado para otros periféricos HAL.</t>
+  </si>
+  <si>
+    <t>Error de inicialización en módulo LEDs.</t>
+  </si>
+  <si>
+    <t>Error de inicialización en botones.</t>
+  </si>
+  <si>
+    <t>Error de inicialización en buzzer.</t>
+  </si>
+  <si>
+    <t>0x0000000008000000</t>
+  </si>
+  <si>
+    <t>ERR_BSP_SENSOR</t>
+  </si>
+  <si>
+    <t>Error en sensores externos de la placa.</t>
+  </si>
+  <si>
+    <t>28-31</t>
+  </si>
+  <si>
+    <t>0x00...10000000 a 80...</t>
+  </si>
+  <si>
+    <t>Reservado para hardware BSP adicional.</t>
+  </si>
+  <si>
+    <t>Voltaje de batería por debajo del límite.</t>
+  </si>
+  <si>
+    <t>Temperatura excesiva en el sistema.</t>
+  </si>
+  <si>
+    <t>Fallo de monitorización de tarea interna.</t>
+  </si>
+  <si>
+    <t>0x0000000800000000</t>
+  </si>
+  <si>
+    <t>ERR_CONFIG_LOAD</t>
+  </si>
+  <si>
+    <t>Error al cargar parámetros de memoria.</t>
+  </si>
+  <si>
+    <t>36-62</t>
+  </si>
+  <si>
+    <t>0x00...10... a 40...</t>
+  </si>
+  <si>
+    <t>Reservado para lógica de aplicación futura.</t>
+  </si>
+  <si>
+    <t>PANIC: Error fatal no recuperable.</t>
   </si>
 </sst>
 </file>
@@ -226,12 +455,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -282,6 +512,20 @@
     <tableColumn id="2" xr3:uid="{1C046501-32EF-4E6C-8421-0F9B0E950E39}" name="Valor"/>
     <tableColumn id="3" xr3:uid="{2F3655B0-6C31-4174-8032-BF4311676566}" name="Disparador Físico (Hardware)"/>
     <tableColumn id="5" xr3:uid="{1B7979C4-886A-44E9-AFC9-82952C41F9E3}" name="Comando UART"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2FF7A2C8-D967-40CB-BCB9-D32FA3B33DBD}" name="Tabla4" displayName="Tabla4" ref="A1:E23" totalsRowShown="0">
+  <autoFilter ref="A1:E23" xr:uid="{2FF7A2C8-D967-40CB-BCB9-D32FA3B33DBD}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{E9517899-C85B-4549-A154-91D577EE7FA9}" name="Categoría"/>
+    <tableColumn id="2" xr3:uid="{D3EE4F90-3B03-4DD4-85BE-5E66C88BDEE1}" name="Bit"/>
+    <tableColumn id="3" xr3:uid="{B18A2EB4-5DB1-4294-9A28-DDC52A26C7B6}" name="Valor Hexadecimal (64-bit)"/>
+    <tableColumn id="4" xr3:uid="{6A207A4F-FEA0-495A-94D0-FA81D114E260}" name="Nombre del Flag"/>
+    <tableColumn id="5" xr3:uid="{1335BA8C-0BD5-42C1-8A9F-212957A68DA7}" name="Descripción / Uso"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -775,7 +1019,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1054,4 +1298,364 @@
     <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B96FE5E-3840-4E53-9D96-FB8328137694}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.5703125" customWidth="1"/>
+    <col min="2" max="2" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="54.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B6" s="3">
+        <v>46119</v>
+      </c>
+      <c r="C6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9">
+        <v>10</v>
+      </c>
+      <c r="C9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10">
+        <v>11</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B11">
+        <v>12</v>
+      </c>
+      <c r="C11" t="s">
+        <v>100</v>
+      </c>
+      <c r="D11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E11" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>103</v>
+      </c>
+      <c r="C12" t="s">
+        <v>104</v>
+      </c>
+      <c r="D12" t="s">
+        <v>94</v>
+      </c>
+      <c r="E12" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13">
+        <v>24</v>
+      </c>
+      <c r="C13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B14">
+        <v>25</v>
+      </c>
+      <c r="C14" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B15">
+        <v>26</v>
+      </c>
+      <c r="C15" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" t="s">
+        <v>76</v>
+      </c>
+      <c r="E15" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <v>27</v>
+      </c>
+      <c r="C16" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" t="s">
+        <v>110</v>
+      </c>
+      <c r="E16" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>112</v>
+      </c>
+      <c r="C17" t="s">
+        <v>113</v>
+      </c>
+      <c r="D17" t="s">
+        <v>94</v>
+      </c>
+      <c r="E17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>77</v>
+      </c>
+      <c r="B18">
+        <v>32</v>
+      </c>
+      <c r="C18" t="s">
+        <v>78</v>
+      </c>
+      <c r="D18" t="s">
+        <v>79</v>
+      </c>
+      <c r="E18" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B19">
+        <v>33</v>
+      </c>
+      <c r="C19" t="s">
+        <v>80</v>
+      </c>
+      <c r="D19" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B20">
+        <v>34</v>
+      </c>
+      <c r="C20" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B21">
+        <v>35</v>
+      </c>
+      <c r="C21" t="s">
+        <v>118</v>
+      </c>
+      <c r="D21" t="s">
+        <v>119</v>
+      </c>
+      <c r="E21" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>121</v>
+      </c>
+      <c r="C22" t="s">
+        <v>122</v>
+      </c>
+      <c r="D22" t="s">
+        <v>94</v>
+      </c>
+      <c r="E22" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>84</v>
+      </c>
+      <c r="B23">
+        <v>63</v>
+      </c>
+      <c r="C23" t="s">
+        <v>85</v>
+      </c>
+      <c r="D23" t="s">
+        <v>86</v>
+      </c>
+      <c r="E23" t="s">
+        <v>124</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>